--- a/applications/ems/SampleExcel/BonusSample.xlsx
+++ b/applications/ems/SampleExcel/BonusSample.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">Comments</t>
   </si>
   <si>
-    <t xml:space="preserve">EMP00000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David</t>
+    <t xml:space="preserve">EMP00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin User</t>
   </si>
   <si>
     <t xml:space="preserve">Approved</t>
@@ -63,9 +63,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -176,7 +177,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -201,7 +202,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -454,7 +463,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.82"/>
@@ -490,43 +499,38 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>2027</v>
-      </c>
-      <c r="F2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F4" s="6"/>
-    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F2:F4" type="list">
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F2" type="list">
       <formula1>Sheet2!$A$1:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2" type="list">
-      <formula1>"2025,2026,2027,2028,2029,2030,2031,2032,2032,2033,2034,2035"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2" type="list">
-      <formula1>"1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2" type="list">
+      <formula1>Sheet2!$C$1:$C$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -568,52 +572,52 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>12</v>
       </c>
     </row>
